--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>91.38355861784534</v>
+        <v>14.84982827539987</v>
       </c>
       <c r="D2" t="n">
-        <v>55.92369962223616</v>
+        <v>9.087601188613375</v>
       </c>
       <c r="E2" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F2" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.4805312681124</v>
+        <v>11.29058633106827</v>
       </c>
       <c r="D3" t="n">
-        <v>51.76251490732442</v>
+        <v>8.411408672440217</v>
       </c>
       <c r="E3" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F3" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.6004843174193</v>
+        <v>7.247578701580637</v>
       </c>
       <c r="D4" t="n">
-        <v>24.26229524799712</v>
+        <v>3.942622977799532</v>
       </c>
       <c r="E4" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F4" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.60610990603664</v>
+        <v>3.673492859730954</v>
       </c>
       <c r="D5" t="n">
-        <v>4.913904280519526</v>
+        <v>0.798509445584423</v>
       </c>
       <c r="E5" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F5" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>78.88211880426327</v>
+        <v>12.81834430569278</v>
       </c>
       <c r="D6" t="n">
-        <v>50.33267655054682</v>
+        <v>8.179059939463858</v>
       </c>
       <c r="E6" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F6" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.91161482622645</v>
+        <v>2.585637409261798</v>
       </c>
       <c r="D7" t="n">
-        <v>2.526205253220726</v>
+        <v>0.410508353648368</v>
       </c>
       <c r="E7" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F7" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.9620804034808</v>
+        <v>6.00633806556563</v>
       </c>
       <c r="D8" t="n">
-        <v>6.740359167059296</v>
+        <v>1.095308364647136</v>
       </c>
       <c r="E8" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F8" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.93548377524759</v>
+        <v>2.264516113477733</v>
       </c>
       <c r="D9" t="n">
-        <v>11.37533205739678</v>
+        <v>1.848491459326977</v>
       </c>
       <c r="E9" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F9" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.74927593898691</v>
+        <v>7.271757340085372</v>
       </c>
       <c r="D10" t="n">
-        <v>20.591260281974</v>
+        <v>3.346079795820776</v>
       </c>
       <c r="E10" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F10" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.28929357888981</v>
+        <v>5.247010206569595</v>
       </c>
       <c r="D11" t="n">
-        <v>12.42129005986293</v>
+        <v>2.018459634727726</v>
       </c>
       <c r="E11" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F11" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>4.688776281070904</v>
+        <v>0.7619261456740219</v>
       </c>
       <c r="D12" t="n">
-        <v>7.044967074067814</v>
+        <v>1.14480714953602</v>
       </c>
       <c r="E12" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F12" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.31335235002643</v>
+        <v>4.438419756879295</v>
       </c>
       <c r="D13" t="n">
-        <v>24.52994635064705</v>
+        <v>3.986116281980145</v>
       </c>
       <c r="E13" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F13" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.74626601023907</v>
+        <v>7.758768226663848</v>
       </c>
       <c r="D14" t="n">
-        <v>34.18102315457337</v>
+        <v>5.554416262618172</v>
       </c>
       <c r="E14" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F14" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.06329967692795</v>
+        <v>3.747786197500793</v>
       </c>
       <c r="D15" t="n">
-        <v>9.821778799910478</v>
+        <v>1.596039054985453</v>
       </c>
       <c r="E15" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F15" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>69.79223610243962</v>
+        <v>11.34123836664644</v>
       </c>
       <c r="D16" t="n">
-        <v>60.89790539380959</v>
+        <v>9.89590962649406</v>
       </c>
       <c r="E16" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F16" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>68.03739546625839</v>
+        <v>11.05607676326699</v>
       </c>
       <c r="D17" t="n">
-        <v>65.93957671821815</v>
+        <v>10.71518121671045</v>
       </c>
       <c r="E17" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F17" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.57799244937802</v>
+        <v>5.293923773023929</v>
       </c>
       <c r="D18" t="n">
-        <v>9.71635735695947</v>
+        <v>1.578908070505914</v>
       </c>
       <c r="E18" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F18" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.31573092558418</v>
+        <v>6.71380627540743</v>
       </c>
       <c r="D19" t="n">
-        <v>20.74808910870375</v>
+        <v>3.371564480164359</v>
       </c>
       <c r="E19" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F19" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>34.95177072026885</v>
+        <v>5.679662742043689</v>
       </c>
       <c r="D20" t="n">
-        <v>34.455788973986</v>
+        <v>5.599065708272725</v>
       </c>
       <c r="E20" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F20" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>22.02651661505255</v>
+        <v>3.57930894994604</v>
       </c>
       <c r="D21" t="n">
-        <v>10.64835843868995</v>
+        <v>1.730358246287117</v>
       </c>
       <c r="E21" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F21" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>22.5238083006496</v>
+        <v>3.66011884885556</v>
       </c>
       <c r="D22" t="n">
-        <v>21.21163302661345</v>
+        <v>3.446890366824686</v>
       </c>
       <c r="E22" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F22" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>5.177974275397572</v>
+        <v>0.8414208197521055</v>
       </c>
       <c r="D23" t="n">
-        <v>2.969005289889781</v>
+        <v>0.4824633596070895</v>
       </c>
       <c r="E23" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F23" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>34.11680800763254</v>
+        <v>5.543981301240288</v>
       </c>
       <c r="D24" t="n">
-        <v>24.45124314948181</v>
+        <v>3.973327011790794</v>
       </c>
       <c r="E24" t="n">
-        <v>22.86646633731293</v>
+        <v>3.715800779813352</v>
       </c>
       <c r="F24" t="n">
-        <v>19.29925355764376</v>
+        <v>3.136128703117111</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
